--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_araucania_provincial.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2022_araucania_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-03 01:39</t>
+    <t xml:space="preserve">2026-10-05 05:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Araucania</t>
+    <t xml:space="preserve">Region de La Araucanía</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
